--- a/data/trans_orig/P6605-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6605-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a tareas repetitivas de menos de 10 minutos /Movimientos repetitivos de manos o brazos en su trabajo en 2007</t>
+          <t>Población según la exposición a tareas repetitivas de menos de 10 minutos /Movimientos repetitivos de manos o brazos en su trabajo en 2007 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61263</t>
+          <t>62247</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94878</t>
+          <t>93011</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29198</t>
+          <t>27570</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50474</t>
+          <t>48836</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96440</t>
+          <t>95114</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>134619</t>
+          <t>133609</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89661</t>
+          <t>90333</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>124715</t>
+          <t>125947</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>42333</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67222</t>
+          <t>66527</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141107</t>
+          <t>140258</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>185752</t>
+          <t>184014</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103483</t>
+          <t>103530</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>141052</t>
+          <t>139656</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29741</t>
+          <t>31627</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50881</t>
+          <t>53232</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>141914</t>
+          <t>140402</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>183682</t>
+          <t>184436</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64862</t>
+          <t>64305</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96689</t>
+          <t>97937</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14851</t>
+          <t>15133</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31528</t>
+          <t>32827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86217</t>
+          <t>85339</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121120</t>
+          <t>121164</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>104775</t>
+          <t>105526</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>145920</t>
+          <t>147331</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57835</t>
+          <t>59426</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>88067</t>
+          <t>89097</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>175111</t>
+          <t>171897</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>226376</t>
+          <t>223135</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114327</t>
+          <t>114852</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156852</t>
+          <t>160016</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50457</t>
+          <t>50637</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79251</t>
+          <t>79713</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175274</t>
+          <t>175880</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>228311</t>
+          <t>228563</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>122764</t>
+          <t>125758</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>165571</t>
+          <t>167892</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56493</t>
+          <t>57892</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86850</t>
+          <t>86528</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>190855</t>
+          <t>191331</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>242811</t>
+          <t>243499</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>131642</t>
+          <t>130380</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>173745</t>
+          <t>174156</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45733</t>
+          <t>45506</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71774</t>
+          <t>75824</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>182871</t>
+          <t>184876</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>237837</t>
+          <t>234566</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132018</t>
+          <t>131157</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>174227</t>
+          <t>172997</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78253</t>
+          <t>77034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>106940</t>
+          <t>107827</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>220322</t>
+          <t>219621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>268928</t>
+          <t>269878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61925</t>
+          <t>62358</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>94978</t>
+          <t>94424</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29194</t>
+          <t>28810</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51043</t>
+          <t>49993</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>95434</t>
+          <t>95517</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>136878</t>
+          <t>137434</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66243</t>
+          <t>66046</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100809</t>
+          <t>99593</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34863</t>
+          <t>34536</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59993</t>
+          <t>59632</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>110112</t>
+          <t>109627</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>149885</t>
+          <t>151313</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78169</t>
+          <t>78796</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115269</t>
+          <t>114596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23681</t>
+          <t>23202</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45890</t>
+          <t>46254</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>108700</t>
+          <t>109497</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>152794</t>
+          <t>151966</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>145333</t>
+          <t>144568</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>187991</t>
+          <t>187000</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>94116</t>
+          <t>95589</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>131812</t>
+          <t>131081</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>250528</t>
+          <t>251520</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>309136</t>
+          <t>307491</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>101389</t>
+          <t>100890</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>139215</t>
+          <t>138207</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71149</t>
+          <t>70730</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>104725</t>
+          <t>105408</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>184532</t>
+          <t>179786</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>233721</t>
+          <t>231916</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>133735</t>
+          <t>131514</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>177769</t>
+          <t>174742</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>96976</t>
+          <t>95112</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>135478</t>
+          <t>131625</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>238594</t>
+          <t>237539</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>296054</t>
+          <t>295754</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>96705</t>
+          <t>97776</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134592</t>
+          <t>135650</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57474</t>
+          <t>58009</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89100</t>
+          <t>89180</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>164396</t>
+          <t>164093</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>214472</t>
+          <t>212076</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>484110</t>
+          <t>484338</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>560919</t>
+          <t>561022</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>287507</t>
+          <t>287696</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>347767</t>
+          <t>346778</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>788171</t>
+          <t>788231</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>885846</t>
+          <t>888929</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>398633</t>
+          <t>400897</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>472109</t>
+          <t>475390</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>220243</t>
+          <t>218532</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>272530</t>
+          <t>275727</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>640525</t>
+          <t>637632</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>730071</t>
+          <t>734217</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>461681</t>
+          <t>465505</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>541155</t>
+          <t>541781</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>245797</t>
+          <t>245867</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>302929</t>
+          <t>300873</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>724906</t>
+          <t>724939</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>824331</t>
+          <t>825722</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>406995</t>
+          <t>408239</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>481146</t>
+          <t>480945</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>163918</t>
+          <t>162162</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>212985</t>
+          <t>212380</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>584254</t>
+          <t>584980</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>675328</t>
+          <t>676047</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a tareas repetitivas de menos de 10 minutos /Movimientos repetitivos de manos o brazos en su trabajo en 2012</t>
+          <t>Población según la exposición a tareas repetitivas de menos de 10 minutos /Movimientos repetitivos de manos o brazos en su trabajo en 2012 (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42985</t>
+          <t>42326</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71350</t>
+          <t>71258</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25968</t>
+          <t>25787</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47486</t>
+          <t>48847</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73131</t>
+          <t>74089</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111398</t>
+          <t>111000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49523</t>
+          <t>49252</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75551</t>
+          <t>76222</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39759</t>
+          <t>38378</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62866</t>
+          <t>63026</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95435</t>
+          <t>93750</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>132215</t>
+          <t>133573</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72983</t>
+          <t>73052</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>104674</t>
+          <t>104371</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36051</t>
+          <t>35162</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59366</t>
+          <t>59221</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116817</t>
+          <t>116576</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>154532</t>
+          <t>154366</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49720</t>
+          <t>49213</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77858</t>
+          <t>76863</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18844</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39103</t>
+          <t>38486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74641</t>
+          <t>74366</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109177</t>
+          <t>108321</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71662</t>
+          <t>70599</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>106056</t>
+          <t>108977</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56151</t>
+          <t>55991</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>86075</t>
+          <t>86737</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>137089</t>
+          <t>138668</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>185889</t>
+          <t>184102</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83746</t>
+          <t>83604</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119610</t>
+          <t>120994</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59984</t>
+          <t>60646</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89979</t>
+          <t>90033</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>152216</t>
+          <t>152468</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198975</t>
+          <t>198238</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103743</t>
+          <t>104273</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143812</t>
+          <t>140922</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56911</t>
+          <t>57054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89481</t>
+          <t>87254</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>171357</t>
+          <t>169829</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>221482</t>
+          <t>219295</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>79007</t>
+          <t>78323</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>114903</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41590</t>
+          <t>40332</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67982</t>
+          <t>68966</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>127717</t>
+          <t>131673</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>173496</t>
+          <t>175216</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59205</t>
+          <t>59531</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90123</t>
+          <t>91157</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44361</t>
+          <t>45064</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72560</t>
+          <t>73691</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>110639</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153520</t>
+          <t>151934</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64195</t>
+          <t>63494</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>97491</t>
+          <t>97016</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36107</t>
+          <t>36527</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>63229</t>
+          <t>63823</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>107284</t>
+          <t>108641</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>149442</t>
+          <t>152690</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84748</t>
+          <t>86571</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121645</t>
+          <t>122075</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40181</t>
+          <t>40767</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67532</t>
+          <t>67064</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133355</t>
+          <t>131338</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>179123</t>
+          <t>177650</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48862</t>
+          <t>49748</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79571</t>
+          <t>79491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43030</t>
+          <t>43491</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70005</t>
+          <t>69614</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>100278</t>
+          <t>98668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>138990</t>
+          <t>140009</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91037</t>
+          <t>90164</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>126483</t>
+          <t>128326</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72048</t>
+          <t>71297</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104500</t>
+          <t>103623</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>171209</t>
+          <t>172770</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>220188</t>
+          <t>221729</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>89188</t>
+          <t>89307</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>124165</t>
+          <t>124536</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65907</t>
+          <t>65025</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>96197</t>
+          <t>97484</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>163467</t>
+          <t>164102</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>212017</t>
+          <t>209391</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>91608</t>
+          <t>93396</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>127617</t>
+          <t>130877</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49107</t>
+          <t>49039</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>81405</t>
+          <t>78469</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>147486</t>
+          <t>149350</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>194731</t>
+          <t>197541</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75383</t>
+          <t>74109</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111104</t>
+          <t>109093</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59511</t>
+          <t>58383</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>87316</t>
+          <t>88080</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>140456</t>
+          <t>141217</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>187429</t>
+          <t>186409</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>292993</t>
+          <t>294010</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>361176</t>
+          <t>358546</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>224100</t>
+          <t>226132</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>283021</t>
+          <t>281686</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>532266</t>
+          <t>532247</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>621372</t>
+          <t>620849</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>318337</t>
+          <t>316338</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>388618</t>
+          <t>385070</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>224918</t>
+          <t>223771</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>279741</t>
+          <t>280337</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>560447</t>
+          <t>561531</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>647262</t>
+          <t>649722</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>391242</t>
+          <t>386194</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>460573</t>
+          <t>459025</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>207654</t>
+          <t>205825</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>261493</t>
+          <t>262483</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>613473</t>
+          <t>612895</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>703979</t>
+          <t>702077</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>278435</t>
+          <t>284974</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>343113</t>
+          <t>352539</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>183821</t>
+          <t>182016</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>238360</t>
+          <t>236733</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>486232</t>
+          <t>482274</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>567411</t>
+          <t>565868</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a tareas repetitivas de menos de 10 minutos /Movimientos repetitivos de manos o brazos en su trabajo en 2016</t>
+          <t>Población según la exposición a tareas repetitivas de menos de 10 minutos /Movimientos repetitivos de manos o brazos en su trabajo en 2016 (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54665</t>
+          <t>52921</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82067</t>
+          <t>81728</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46863</t>
+          <t>47124</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69662</t>
+          <t>70615</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107070</t>
+          <t>105336</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>143164</t>
+          <t>143225</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>53418</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80695</t>
+          <t>79874</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27166</t>
+          <t>28645</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49824</t>
+          <t>50593</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89491</t>
+          <t>88852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125225</t>
+          <t>122637</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54348</t>
+          <t>54398</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>83044</t>
+          <t>84052</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26443</t>
+          <t>26655</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46559</t>
+          <t>47051</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>85313</t>
+          <t>83485</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>121247</t>
+          <t>117865</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29027</t>
+          <t>28305</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53553</t>
+          <t>52986</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25494</t>
+          <t>24336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46908</t>
+          <t>45023</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59421</t>
+          <t>58814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91596</t>
+          <t>91514</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>111498</t>
+          <t>113524</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>151635</t>
+          <t>152801</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77585</t>
+          <t>75950</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>108341</t>
+          <t>106459</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>200554</t>
+          <t>197483</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>253291</t>
+          <t>248608</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80825</t>
+          <t>81340</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116414</t>
+          <t>116242</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59799</t>
+          <t>60252</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89098</t>
+          <t>88904</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149595</t>
+          <t>148975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195554</t>
+          <t>193948</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93171</t>
+          <t>91946</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>132978</t>
+          <t>130201</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47938</t>
+          <t>48239</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75032</t>
+          <t>77048</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>151449</t>
+          <t>148756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>196671</t>
+          <t>195957</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57481</t>
+          <t>55581</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88945</t>
+          <t>86501</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34366</t>
+          <t>34004</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59573</t>
+          <t>59514</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>96754</t>
+          <t>96578</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>136356</t>
+          <t>137259</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54270</t>
+          <t>53491</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>84574</t>
+          <t>84499</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51642</t>
+          <t>50304</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78285</t>
+          <t>79682</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111686</t>
+          <t>112295</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152398</t>
+          <t>153404</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85087</t>
+          <t>86288</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>120740</t>
+          <t>123086</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66118</t>
+          <t>65687</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>95368</t>
+          <t>94796</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>157540</t>
+          <t>159065</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>207655</t>
+          <t>206536</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80579</t>
+          <t>79892</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>114536</t>
+          <t>115364</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58277</t>
+          <t>58008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87454</t>
+          <t>88000</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>147301</t>
+          <t>147127</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>193308</t>
+          <t>192670</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78027</t>
+          <t>79191</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114509</t>
+          <t>113161</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42081</t>
+          <t>42739</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68411</t>
+          <t>68639</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>130268</t>
+          <t>128541</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>174932</t>
+          <t>174880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>124496</t>
+          <t>124433</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>162984</t>
+          <t>163335</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>106667</t>
+          <t>108512</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>143706</t>
+          <t>145950</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>246665</t>
+          <t>243952</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>299367</t>
+          <t>296591</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,09%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>65032</t>
+          <t>65012</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>98136</t>
+          <t>96769</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55346</t>
+          <t>53207</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>84344</t>
+          <t>82929</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127010</t>
+          <t>128668</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>171978</t>
+          <t>173967</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89664</t>
+          <t>91271</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>126501</t>
+          <t>126985</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>45166</t>
+          <t>46843</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>73129</t>
+          <t>73639</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>144724</t>
+          <t>144454</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>190283</t>
+          <t>190593</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51330</t>
+          <t>51186</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>81346</t>
+          <t>79843</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55981</t>
+          <t>55057</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86436</t>
+          <t>88279</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>113703</t>
+          <t>114495</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>157148</t>
+          <t>155447</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>376302</t>
+          <t>379801</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>442931</t>
+          <t>447148</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>311551</t>
+          <t>311524</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>372331</t>
+          <t>368571</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706499</t>
+          <t>707249</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>801744</t>
+          <t>797309</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,59%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>315542</t>
+          <t>315524</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>383156</t>
+          <t>382474</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>232056</t>
+          <t>233148</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>288957</t>
+          <t>289165</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>563408</t>
+          <t>565270</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>650014</t>
+          <t>656060</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>350763</t>
+          <t>346295</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>416564</t>
+          <t>417012</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>203569</t>
+          <t>202993</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>254055</t>
+          <t>254512</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>565028</t>
+          <t>566196</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>650574</t>
+          <t>649953</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>241186</t>
+          <t>239442</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>301626</t>
+          <t>300797</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>179092</t>
+          <t>181255</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>230879</t>
+          <t>233189</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>434428</t>
+          <t>435469</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>512593</t>
+          <t>517445</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a tareas repetitivas de menos de 10 minutos /Movimientos repetitivos de manos o brazos en su trabajo en 2023</t>
+          <t>Población según la exposición a tareas repetitivas de menos de 10 minutos /Movimientos repetitivos de manos o brazos en su trabajo en 2023 (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24038</t>
+          <t>25508</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51925</t>
+          <t>53379</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15311</t>
+          <t>14817</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31923</t>
+          <t>32753</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44825</t>
+          <t>44436</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76967</t>
+          <t>74999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35758</t>
+          <t>33085</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60042</t>
+          <t>58099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32844</t>
+          <t>31843</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49668</t>
+          <t>49278</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>71428</t>
+          <t>71181</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101568</t>
+          <t>102125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42090</t>
+          <t>43229</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73039</t>
+          <t>73345</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27963</t>
+          <t>27490</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44379</t>
+          <t>43988</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>75143</t>
+          <t>77533</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>110416</t>
+          <t>109918</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21215</t>
+          <t>22917</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48454</t>
+          <t>47228</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18771</t>
+          <t>18386</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35647</t>
+          <t>35557</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45443</t>
+          <t>45740</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75595</t>
+          <t>77232</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>125842</t>
+          <t>121334</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>467855</t>
+          <t>460101</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37615</t>
+          <t>38048</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59003</t>
+          <t>58251</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>170475</t>
+          <t>170544</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>586169</t>
+          <t>569844</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>76,47%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27322</t>
+          <t>24425</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142287</t>
+          <t>144314</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55749</t>
+          <t>56309</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77880</t>
+          <t>78158</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53623</t>
+          <t>66382</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215988</t>
+          <t>219274</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36018</t>
+          <t>39319</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>219949</t>
+          <t>222905</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45115</t>
+          <t>44875</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66482</t>
+          <t>65950</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>68531</t>
+          <t>72441</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>262835</t>
+          <t>263106</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,31%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73862</t>
+          <t>74897</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24284</t>
+          <t>24732</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43981</t>
+          <t>44420</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25524</t>
+          <t>24815</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112858</t>
+          <t>109025</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39293</t>
+          <t>38602</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64076</t>
+          <t>64293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24787</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62980</t>
+          <t>62638</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70080</t>
+          <t>68214</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>117317</t>
+          <t>116556</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,67%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48480</t>
+          <t>47419</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>76218</t>
+          <t>76570</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>21967</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54711</t>
+          <t>55397</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>70524</t>
+          <t>70635</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>123191</t>
+          <t>125952</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>22446</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43769</t>
+          <t>43140</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10122</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31192</t>
+          <t>32728</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36698</t>
+          <t>36336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68190</t>
+          <t>68699</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18164</t>
+          <t>17776</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41450</t>
+          <t>40956</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25990</t>
+          <t>26346</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105481</t>
+          <t>107158</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>159502</t>
+          <t>164161</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>48,83%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68789</t>
+          <t>67666</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>98916</t>
+          <t>98817</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59702</t>
+          <t>59631</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81881</t>
+          <t>82626</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>136100</t>
+          <t>133607</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>174453</t>
+          <t>171936</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41296</t>
+          <t>41301</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68393</t>
+          <t>68354</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38089</t>
+          <t>37595</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59468</t>
+          <t>58958</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85461</t>
+          <t>84191</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>120316</t>
+          <t>118786</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47969</t>
+          <t>48131</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>76004</t>
+          <t>77318</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33573</t>
+          <t>34877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>54097</t>
+          <t>54717</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>89661</t>
+          <t>88628</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>122964</t>
+          <t>124673</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19268</t>
+          <t>18357</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39424</t>
+          <t>41021</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18223</t>
+          <t>18208</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34063</t>
+          <t>34967</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41961</t>
+          <t>40984</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68027</t>
+          <t>68969</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>303503</t>
+          <t>299884</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>786304</t>
+          <t>761060</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>158549</t>
+          <t>154409</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>209763</t>
+          <t>208309</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>481450</t>
+          <t>481879</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1054215</t>
+          <t>1089262</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>60,79%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>119620</t>
+          <t>132119</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>314424</t>
+          <t>312860</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>164554</t>
+          <t>164478</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>219081</t>
+          <t>218446</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>273371</t>
+          <t>277191</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>513448</t>
+          <t>517727</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>137440</t>
+          <t>139237</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>349351</t>
+          <t>351118</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>128333</t>
+          <t>132020</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>176014</t>
+          <t>178819</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>280532</t>
+          <t>270240</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>502338</t>
+          <t>507803</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>66212</t>
+          <t>65346</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>170180</t>
+          <t>171300</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>107552</t>
+          <t>108295</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>224314</t>
+          <t>270483</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>175451</t>
+          <t>177175</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>354603</t>
+          <t>350453</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6605-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6605-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62247</t>
+          <t>60729</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93011</t>
+          <t>91844</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27570</t>
+          <t>28512</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48836</t>
+          <t>49530</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95114</t>
+          <t>94654</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133609</t>
+          <t>132740</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90333</t>
+          <t>89687</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125947</t>
+          <t>125099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42333</t>
+          <t>44035</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66527</t>
+          <t>68326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140258</t>
+          <t>140005</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>184014</t>
+          <t>183995</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103530</t>
+          <t>104351</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>139656</t>
+          <t>142733</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31627</t>
+          <t>30297</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53232</t>
+          <t>53542</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>140402</t>
+          <t>142566</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>184436</t>
+          <t>185136</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,24%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64305</t>
+          <t>63698</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97937</t>
+          <t>96388</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15133</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32827</t>
+          <t>33379</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85339</t>
+          <t>83706</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121164</t>
+          <t>120371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>105526</t>
+          <t>107535</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>147331</t>
+          <t>147376</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59426</t>
+          <t>58082</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89097</t>
+          <t>88062</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>171897</t>
+          <t>175077</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>223135</t>
+          <t>225980</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114852</t>
+          <t>115424</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160016</t>
+          <t>158435</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50637</t>
+          <t>51949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79713</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175880</t>
+          <t>177384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>228563</t>
+          <t>227187</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125758</t>
+          <t>123769</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>167892</t>
+          <t>165997</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57892</t>
+          <t>57781</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86528</t>
+          <t>87748</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>191331</t>
+          <t>191226</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>243499</t>
+          <t>242189</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>130380</t>
+          <t>130751</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>174156</t>
+          <t>174107</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45506</t>
+          <t>45417</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75824</t>
+          <t>73617</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>184876</t>
+          <t>187331</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>234566</t>
+          <t>237595</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>131157</t>
+          <t>131792</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172997</t>
+          <t>171045</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77034</t>
+          <t>77765</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107827</t>
+          <t>107498</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>219621</t>
+          <t>221604</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>269878</t>
+          <t>272115</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>44,0%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62358</t>
+          <t>60180</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>94424</t>
+          <t>94062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28810</t>
+          <t>28688</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49993</t>
+          <t>50357</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>95517</t>
+          <t>96206</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>137434</t>
+          <t>135980</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66046</t>
+          <t>68042</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99593</t>
+          <t>99965</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34536</t>
+          <t>34813</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59632</t>
+          <t>60646</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109627</t>
+          <t>108941</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>151313</t>
+          <t>153105</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78796</t>
+          <t>77832</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114596</t>
+          <t>114981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23202</t>
+          <t>23562</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46254</t>
+          <t>44540</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>109497</t>
+          <t>110555</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>151966</t>
+          <t>154163</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>144568</t>
+          <t>144758</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>187000</t>
+          <t>185409</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>95589</t>
+          <t>97584</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>131081</t>
+          <t>132694</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>251520</t>
+          <t>253847</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>307491</t>
+          <t>309630</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>100890</t>
+          <t>103491</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>138207</t>
+          <t>140678</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70730</t>
+          <t>72671</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>105408</t>
+          <t>105986</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>179786</t>
+          <t>185402</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>231916</t>
+          <t>237159</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,21%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>131514</t>
+          <t>132969</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>174742</t>
+          <t>174140</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>95112</t>
+          <t>94948</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>131625</t>
+          <t>130730</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>237539</t>
+          <t>238076</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>295754</t>
+          <t>292447</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97776</t>
+          <t>96111</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>135650</t>
+          <t>134586</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58009</t>
+          <t>59234</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89180</t>
+          <t>90961</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>164093</t>
+          <t>161950</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>212076</t>
+          <t>213828</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>484338</t>
+          <t>478224</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>561022</t>
+          <t>559312</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>287696</t>
+          <t>286154</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>346778</t>
+          <t>346328</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>788231</t>
+          <t>791048</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>888929</t>
+          <t>888102</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>400897</t>
+          <t>404142</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>475390</t>
+          <t>474413</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>218532</t>
+          <t>222120</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>275727</t>
+          <t>272839</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>637632</t>
+          <t>637017</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>734217</t>
+          <t>731039</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>465505</t>
+          <t>465842</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>541781</t>
+          <t>540784</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>245867</t>
+          <t>242177</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>300873</t>
+          <t>301902</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>724939</t>
+          <t>726680</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>825722</t>
+          <t>826448</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>408239</t>
+          <t>405585</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>480945</t>
+          <t>482468</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>162162</t>
+          <t>162820</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>212380</t>
+          <t>213322</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>584980</t>
+          <t>585698</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>676047</t>
+          <t>674317</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42326</t>
+          <t>42329</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71258</t>
+          <t>73029</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25787</t>
+          <t>25812</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48847</t>
+          <t>47913</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74089</t>
+          <t>74963</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111000</t>
+          <t>111199</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49252</t>
+          <t>49503</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76222</t>
+          <t>78355</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38378</t>
+          <t>38220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63026</t>
+          <t>62147</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93750</t>
+          <t>93898</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>133573</t>
+          <t>130821</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73052</t>
+          <t>73770</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>104371</t>
+          <t>104459</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35162</t>
+          <t>34769</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59221</t>
+          <t>59514</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116576</t>
+          <t>115307</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>154366</t>
+          <t>154867</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49213</t>
+          <t>50070</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76863</t>
+          <t>79100</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>18450</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38486</t>
+          <t>38506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74366</t>
+          <t>75562</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108321</t>
+          <t>109473</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70599</t>
+          <t>72053</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>108977</t>
+          <t>108575</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55991</t>
+          <t>55189</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>86737</t>
+          <t>87013</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>138668</t>
+          <t>135839</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>184102</t>
+          <t>183568</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83604</t>
+          <t>84019</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120994</t>
+          <t>120858</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60646</t>
+          <t>60184</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90033</t>
+          <t>90157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>152468</t>
+          <t>154163</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198238</t>
+          <t>197690</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104273</t>
+          <t>104353</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>140922</t>
+          <t>142658</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57054</t>
+          <t>56680</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87254</t>
+          <t>87153</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>169829</t>
+          <t>169940</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>219295</t>
+          <t>218630</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78323</t>
+          <t>79115</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>114147</t>
+          <t>115124</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40332</t>
+          <t>41668</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68966</t>
+          <t>69621</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>131673</t>
+          <t>130614</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>175216</t>
+          <t>174710</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59531</t>
+          <t>57162</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91157</t>
+          <t>90257</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45064</t>
+          <t>44041</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73691</t>
+          <t>72703</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>110639</t>
+          <t>109105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151934</t>
+          <t>151737</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63494</t>
+          <t>63766</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>97016</t>
+          <t>97563</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36527</t>
+          <t>36936</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>63823</t>
+          <t>62760</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>108641</t>
+          <t>108566</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>152690</t>
+          <t>151992</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86571</t>
+          <t>85692</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122075</t>
+          <t>120740</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40767</t>
+          <t>40680</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67064</t>
+          <t>67303</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>131338</t>
+          <t>133964</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>177650</t>
+          <t>178704</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49748</t>
+          <t>49607</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79491</t>
+          <t>78851</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43491</t>
+          <t>43770</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69614</t>
+          <t>70600</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>98668</t>
+          <t>99459</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140009</t>
+          <t>139259</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90164</t>
+          <t>91556</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>128326</t>
+          <t>129834</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>71297</t>
+          <t>71760</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103623</t>
+          <t>102487</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>172770</t>
+          <t>170872</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>221729</t>
+          <t>221955</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>89307</t>
+          <t>90486</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>124536</t>
+          <t>126143</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65025</t>
+          <t>65359</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>97484</t>
+          <t>96474</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>164102</t>
+          <t>165445</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>209391</t>
+          <t>212789</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>93396</t>
+          <t>91217</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>130877</t>
+          <t>128237</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49039</t>
+          <t>49879</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>78469</t>
+          <t>76981</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>149350</t>
+          <t>150493</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>197541</t>
+          <t>195766</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>74109</t>
+          <t>74549</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>109093</t>
+          <t>111078</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58383</t>
+          <t>59972</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88080</t>
+          <t>88043</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>141217</t>
+          <t>141806</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>186409</t>
+          <t>187888</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>294010</t>
+          <t>295078</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>358546</t>
+          <t>364178</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>226132</t>
+          <t>222019</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>281686</t>
+          <t>282144</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>532247</t>
+          <t>535641</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>620849</t>
+          <t>618748</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>316338</t>
+          <t>316876</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>385070</t>
+          <t>387111</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>223771</t>
+          <t>223201</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>280337</t>
+          <t>280313</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>561531</t>
+          <t>561006</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>649722</t>
+          <t>646728</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>386194</t>
+          <t>390120</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>459025</t>
+          <t>460532</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>205825</t>
+          <t>208750</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>262483</t>
+          <t>265606</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>612895</t>
+          <t>613613</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>702077</t>
+          <t>702147</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>284974</t>
+          <t>283954</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>352539</t>
+          <t>348894</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>182016</t>
+          <t>184266</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>236733</t>
+          <t>239466</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>482274</t>
+          <t>485181</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>565868</t>
+          <t>567264</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52921</t>
+          <t>53406</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81728</t>
+          <t>81442</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>47411</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70615</t>
+          <t>70474</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105336</t>
+          <t>107872</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>143225</t>
+          <t>145791</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53418</t>
+          <t>54374</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79874</t>
+          <t>80054</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28645</t>
+          <t>28638</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50593</t>
+          <t>50442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88852</t>
+          <t>89163</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122637</t>
+          <t>124005</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54398</t>
+          <t>54317</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84052</t>
+          <t>81640</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>27082</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47051</t>
+          <t>46156</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83485</t>
+          <t>85702</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>117865</t>
+          <t>120514</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28305</t>
+          <t>29830</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52986</t>
+          <t>53598</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24336</t>
+          <t>24606</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45023</t>
+          <t>46126</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58814</t>
+          <t>59762</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91514</t>
+          <t>91634</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>113524</t>
+          <t>112372</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>152801</t>
+          <t>152699</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75950</t>
+          <t>77162</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>106459</t>
+          <t>108877</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>197483</t>
+          <t>198602</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>248608</t>
+          <t>252579</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,97%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81340</t>
+          <t>81274</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116242</t>
+          <t>116666</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60252</t>
+          <t>60227</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88904</t>
+          <t>89925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148975</t>
+          <t>151211</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>193948</t>
+          <t>196847</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91946</t>
+          <t>92766</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>130201</t>
+          <t>130756</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48239</t>
+          <t>48679</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77048</t>
+          <t>75782</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>148756</t>
+          <t>149258</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>195957</t>
+          <t>197002</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55581</t>
+          <t>54621</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86501</t>
+          <t>86804</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34004</t>
+          <t>33124</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59514</t>
+          <t>59393</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>96578</t>
+          <t>97065</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>137259</t>
+          <t>136938</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53491</t>
+          <t>54598</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>84499</t>
+          <t>84629</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50304</t>
+          <t>50558</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79682</t>
+          <t>79378</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>112295</t>
+          <t>111576</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153404</t>
+          <t>154264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86288</t>
+          <t>83734</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>123086</t>
+          <t>119996</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65687</t>
+          <t>65899</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>94796</t>
+          <t>94932</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>159065</t>
+          <t>158919</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>206536</t>
+          <t>205903</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>79892</t>
+          <t>79524</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115364</t>
+          <t>115732</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58008</t>
+          <t>57184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88000</t>
+          <t>85416</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>147127</t>
+          <t>148572</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>192670</t>
+          <t>192293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79191</t>
+          <t>77620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>113161</t>
+          <t>113473</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42739</t>
+          <t>41784</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68639</t>
+          <t>68543</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>128541</t>
+          <t>128481</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>174880</t>
+          <t>170798</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>124433</t>
+          <t>125488</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>163335</t>
+          <t>163791</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>108512</t>
+          <t>109198</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>145950</t>
+          <t>146476</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>243952</t>
+          <t>245062</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>296591</t>
+          <t>299482</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,49%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>65012</t>
+          <t>65489</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96769</t>
+          <t>97704</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53207</t>
+          <t>54437</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>82929</t>
+          <t>85246</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>128668</t>
+          <t>128959</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>173967</t>
+          <t>172332</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>91271</t>
+          <t>91357</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>126985</t>
+          <t>125964</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46843</t>
+          <t>46429</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>73639</t>
+          <t>73215</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>144454</t>
+          <t>145599</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>190593</t>
+          <t>188935</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51186</t>
+          <t>50152</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79843</t>
+          <t>80138</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55057</t>
+          <t>54522</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88279</t>
+          <t>84918</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>114495</t>
+          <t>114715</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>155447</t>
+          <t>155697</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>379801</t>
+          <t>378616</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>447148</t>
+          <t>446893</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>311524</t>
+          <t>309301</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>368571</t>
+          <t>370489</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707249</t>
+          <t>708234</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>797309</t>
+          <t>796359</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>315524</t>
+          <t>316145</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>382474</t>
+          <t>382817</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>233148</t>
+          <t>232466</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>289165</t>
+          <t>289427</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>565270</t>
+          <t>569309</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>656060</t>
+          <t>652410</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>346295</t>
+          <t>348683</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>417012</t>
+          <t>418033</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>202993</t>
+          <t>201749</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>254512</t>
+          <t>255340</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>566196</t>
+          <t>565704</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>649953</t>
+          <t>653815</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>239442</t>
+          <t>241198</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>300797</t>
+          <t>302350</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>181255</t>
+          <t>181048</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>233189</t>
+          <t>233643</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>435469</t>
+          <t>435252</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>517445</t>
+          <t>513567</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>36656</t>
+          <t>42023</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25508</t>
+          <t>28406</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53379</t>
+          <t>57661</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>23202</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14817</t>
+          <t>15626</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32753</t>
+          <t>33188</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>58609</t>
+          <t>65226</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44436</t>
+          <t>50584</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74999</t>
+          <t>85974</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46157</t>
+          <t>50334</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33085</t>
+          <t>37710</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58099</t>
+          <t>63291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40327</t>
+          <t>43290</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31843</t>
+          <t>35268</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49278</t>
+          <t>53384</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>86484</t>
+          <t>93624</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>71181</t>
+          <t>79713</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>102125</t>
+          <t>109364</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56226</t>
+          <t>61356</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43229</t>
+          <t>47281</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73345</t>
+          <t>76535</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35935</t>
+          <t>40086</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27490</t>
+          <t>31550</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43988</t>
+          <t>50223</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>92161</t>
+          <t>101442</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>77533</t>
+          <t>84349</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109918</t>
+          <t>117430</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33131</t>
+          <t>39754</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22917</t>
+          <t>27393</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47228</t>
+          <t>54283</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26141</t>
+          <t>30790</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18386</t>
+          <t>22423</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35557</t>
+          <t>40978</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>59273</t>
+          <t>70545</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45740</t>
+          <t>54601</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77232</t>
+          <t>87647</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>317077</t>
+          <t>83043</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>121334</t>
+          <t>66445</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>460101</t>
+          <t>101599</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47729</t>
+          <t>52559</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38048</t>
+          <t>42033</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58251</t>
+          <t>64472</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>364806</t>
+          <t>135601</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>170544</t>
+          <t>115890</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>569844</t>
+          <t>158601</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74052</t>
+          <t>82784</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24425</t>
+          <t>66075</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144314</t>
+          <t>100389</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>66652</t>
+          <t>71934</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56309</t>
+          <t>59920</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78158</t>
+          <t>83102</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>140704</t>
+          <t>154717</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66382</t>
+          <t>134673</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>219274</t>
+          <t>175672</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>115568</t>
+          <t>123601</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39319</t>
+          <t>104261</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>222905</t>
+          <t>143239</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54978</t>
+          <t>58946</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44875</t>
+          <t>47824</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65950</t>
+          <t>70835</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>170546</t>
+          <t>182548</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72441</t>
+          <t>161645</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>263106</t>
+          <t>205776</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35906</t>
+          <t>43864</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>29151</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74897</t>
+          <t>62068</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33265</t>
+          <t>37238</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24732</t>
+          <t>28219</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44420</t>
+          <t>50935</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>69171</t>
+          <t>81102</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24815</t>
+          <t>65387</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>109025</t>
+          <t>103039</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>542603</t>
+          <t>333292</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>542603</t>
+          <t>333292</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>542603</t>
+          <t>333292</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>202623</t>
+          <t>220677</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>202623</t>
+          <t>220677</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202623</t>
+          <t>220677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>745227</t>
+          <t>553968</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>745227</t>
+          <t>553968</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>745227</t>
+          <t>553968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>50395</t>
+          <t>57022</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38602</t>
+          <t>42075</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64293</t>
+          <t>72296</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>46426</t>
+          <t>56509</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>45914</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62638</t>
+          <t>67680</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>96821</t>
+          <t>113531</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68214</t>
+          <t>95307</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116556</t>
+          <t>132897</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>37,34%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62096</t>
+          <t>62989</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47419</t>
+          <t>48092</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>76570</t>
+          <t>79384</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40665</t>
+          <t>45086</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21967</t>
+          <t>36635</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55397</t>
+          <t>55508</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>102761</t>
+          <t>108076</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>70635</t>
+          <t>90185</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>125952</t>
+          <t>128155</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>31546</t>
+          <t>42118</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22446</t>
+          <t>29622</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43140</t>
+          <t>55809</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>21313</t>
+          <t>26311</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>18159</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32728</t>
+          <t>34930</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>52859</t>
+          <t>68429</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36336</t>
+          <t>54781</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68699</t>
+          <t>85924</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>40081</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17776</t>
+          <t>27627</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40956</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>56507</t>
+          <t>25761</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26346</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107158</t>
+          <t>35236</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>83735</t>
+          <t>65842</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>51075</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>164161</t>
+          <t>87289</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>171265</t>
+          <t>202210</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>171265</t>
+          <t>202210</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>171265</t>
+          <t>202210</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>336176</t>
+          <t>355878</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>336176</t>
+          <t>355878</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>336176</t>
+          <t>355878</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>83152</t>
+          <t>96903</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67666</t>
+          <t>82737</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>98817</t>
+          <t>114801</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>70181</t>
+          <t>79017</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59631</t>
+          <t>67943</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82626</t>
+          <t>91407</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>153333</t>
+          <t>175920</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>133607</t>
+          <t>156808</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>171936</t>
+          <t>197313</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>53435</t>
+          <t>55055</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41301</t>
+          <t>40940</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68354</t>
+          <t>69014</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>48284</t>
+          <t>53113</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37595</t>
+          <t>42562</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58958</t>
+          <t>64977</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>101718</t>
+          <t>108168</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>84191</t>
+          <t>91646</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118786</t>
+          <t>127398</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>61040</t>
+          <t>63626</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48131</t>
+          <t>50141</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77318</t>
+          <t>78053</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>44389</t>
+          <t>47750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34877</t>
+          <t>35757</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>54717</t>
+          <t>59261</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>105429</t>
+          <t>111376</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>88628</t>
+          <t>95397</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>124673</t>
+          <t>131379</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>28159</t>
+          <t>32534</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18357</t>
+          <t>22486</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41021</t>
+          <t>45451</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>25200</t>
+          <t>28785</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18208</t>
+          <t>20577</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34967</t>
+          <t>38457</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>53359</t>
+          <t>61320</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40984</t>
+          <t>47053</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68969</t>
+          <t>77003</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>487280</t>
+          <t>278991</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>299884</t>
+          <t>247276</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>761060</t>
+          <t>312326</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>186288</t>
+          <t>211286</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>154409</t>
+          <t>189409</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>208309</t>
+          <t>232743</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>673568</t>
+          <t>490278</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>481879</t>
+          <t>449872</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1089262</t>
+          <t>527298</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>235739</t>
+          <t>251163</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132119</t>
+          <t>222398</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>312860</t>
+          <t>285990</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>195928</t>
+          <t>213423</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>164478</t>
+          <t>195177</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>218446</t>
+          <t>236940</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>431667</t>
+          <t>464585</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>277191</t>
+          <t>427042</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>517727</t>
+          <t>501266</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>264380</t>
+          <t>290701</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>139237</t>
+          <t>256822</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>351118</t>
+          <t>319474</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>156615</t>
+          <t>173094</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>132020</t>
+          <t>153341</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>178819</t>
+          <t>194872</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>420995</t>
+          <t>463795</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>270240</t>
+          <t>429478</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>507803</t>
+          <t>503102</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>124425</t>
+          <t>156233</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>65346</t>
+          <t>129827</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>171300</t>
+          <t>184418</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>141113</t>
+          <t>122575</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>108295</t>
+          <t>105248</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>270483</t>
+          <t>142384</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>265538</t>
+          <t>278808</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>177175</t>
+          <t>247077</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>350453</t>
+          <t>314309</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1111825</t>
+          <t>977089</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1111825</t>
+          <t>977089</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1111825</t>
+          <t>977089</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1791769</t>
+          <t>1697467</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1791769</t>
+          <t>1697467</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1791769</t>
+          <t>1697467</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
